--- a/Docs/Items.xlsx
+++ b/Docs/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -135,9 +135,6 @@
     <t>Conductive, Unscoring</t>
   </si>
   <si>
-    <t>Vulnerable:Fire, Explosive, Unscoring</t>
-  </si>
-  <si>
     <t>Small war hammer</t>
   </si>
   <si>
@@ -256,6 +253,9 @@
   </si>
   <si>
     <t>Deal 2 (Physical) damage to the target</t>
+  </si>
+  <si>
+    <t>Vulnerable:Fire, Explosive (1), Unscoring</t>
   </si>
 </sst>
 </file>
@@ -467,38 +467,38 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -806,43 +806,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M62"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="4"/>
+    <col min="1" max="1" width="8.88671875" style="4"/>
     <col min="2" max="2" width="5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="25.42578125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="3.85546875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="46.28515625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="40.42578125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="32.42578125" style="4" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" style="4"/>
-    <col min="13" max="13" width="5.140625" style="4" customWidth="1"/>
-    <col min="14" max="16384" width="8.85546875" style="4"/>
+    <col min="3" max="3" width="7.88671875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="25.44140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="3.88671875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="46.33203125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="40.44140625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="32.44140625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" style="4" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" style="4"/>
+    <col min="13" max="13" width="5.109375" style="4" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-    </row>
-    <row r="4" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -882,7 +882,7 @@
         <v>6</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H5"/>
       <c r="I5" s="7" t="s">
@@ -892,7 +892,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="46.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>34</v>
       </c>
@@ -901,7 +901,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:13" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -922,7 +922,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="1:13" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="6" t="s">
         <v>6</v>
       </c>
@@ -940,7 +940,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9" s="5"/>
@@ -950,7 +950,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C10" s="6" t="s">
         <v>0</v>
       </c>
@@ -962,25 +962,25 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
     </row>
-    <row r="11" spans="1:13" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="28.95" x14ac:dyDescent="0.3">
       <c r="C11" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C13" s="6" t="s">
         <v>0</v>
       </c>
@@ -1013,11 +1013,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C14" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="28" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C14" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="29" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="5"/>
@@ -1037,49 +1037,49 @@
         <v>27</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M14" s="9">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C15" s="28"/>
+      <c r="D15" s="29"/>
       <c r="E15" s="5"/>
       <c r="F15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="24" t="s">
+      <c r="G15" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="26"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="27"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C16" s="28"/>
+      <c r="D16" s="29"/>
       <c r="F16" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="26"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="G16" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="27"/>
+    </row>
+    <row r="17" spans="3:13" ht="15" x14ac:dyDescent="0.25">
       <c r="C17"/>
       <c r="D17"/>
       <c r="E17" s="5"/>
@@ -1114,7 +1114,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:13" ht="15" x14ac:dyDescent="0.25">
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -1124,7 +1124,7 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
     </row>
-    <row r="21" spans="3:13" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:13" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="11" t="s">
         <v>0</v>
       </c>
@@ -1157,11 +1157,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="22" t="s">
+    <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="24" t="s">
         <v>36</v>
       </c>
       <c r="E22"/>
@@ -1175,56 +1175,56 @@
         <v>0</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J22" s="12" t="s">
         <v>27</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M22" s="12">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C23" s="21"/>
-      <c r="D23" s="22"/>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C23" s="31"/>
+      <c r="D23" s="24"/>
       <c r="E23"/>
       <c r="F23" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="G23" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C24" s="21"/>
-      <c r="D24" s="22"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C24" s="31"/>
+      <c r="D24" s="24"/>
       <c r="E24"/>
       <c r="F24" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="22"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="24"/>
+    </row>
+    <row r="25" spans="3:13" ht="15" x14ac:dyDescent="0.25">
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -1234,12 +1234,12 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
     </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:13" ht="15" x14ac:dyDescent="0.25">
       <c r="C26" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -1248,12 +1248,12 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C27" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>79</v>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C27" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>78</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -1262,9 +1262,9 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C28" s="21"/>
-      <c r="D28" s="22"/>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C28" s="31"/>
+      <c r="D28" s="24"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -1272,9 +1272,9 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
     </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C29" s="21"/>
-      <c r="D29" s="22"/>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C29" s="31"/>
+      <c r="D29" s="24"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -1282,7 +1282,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
     </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:13" ht="15" x14ac:dyDescent="0.25">
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
@@ -1292,19 +1292,19 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
     </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:13" ht="15" x14ac:dyDescent="0.25">
       <c r="C31" s="18" t="s">
         <v>0</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="18" t="s">
         <v>0</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -1313,19 +1313,19 @@
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
     </row>
-    <row r="32" spans="3:13" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="18" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="18" t="s">
         <v>6</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -1334,7 +1334,7 @@
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
     </row>
-    <row r="33" spans="3:13" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:13" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33"/>
@@ -1347,7 +1347,7 @@
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
     </row>
-    <row r="34" spans="3:13" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:13" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34"/>
@@ -1360,7 +1360,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
     </row>
-    <row r="35" spans="3:13" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:13" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -1373,12 +1373,12 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
     </row>
-    <row r="36" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="16" t="s">
@@ -1411,69 +1411,69 @@
         <v>6</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G37" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="H37" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="H37" s="16" t="s">
-        <v>47</v>
-      </c>
       <c r="I37" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J37" s="16" t="s">
         <v>27</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M37" s="16">
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C38" s="15"/>
       <c r="D38" s="16"/>
       <c r="E38" s="5"/>
       <c r="F38" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="G38" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="30"/>
-      <c r="K38" s="30"/>
-      <c r="L38" s="30"/>
-      <c r="M38" s="31"/>
-    </row>
-    <row r="39" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="G38" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="23"/>
+    </row>
+    <row r="39" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C39" s="15"/>
       <c r="D39" s="16"/>
       <c r="E39" s="5"/>
       <c r="F39" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G39" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="30"/>
-      <c r="L39" s="30"/>
-      <c r="M39" s="31"/>
-    </row>
-    <row r="40" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G39" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="23"/>
+    </row>
+    <row r="40" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -1486,12 +1486,12 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
     </row>
-    <row r="41" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C41" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -1503,12 +1503,12 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
     </row>
-    <row r="42" spans="3:13" ht="50.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:13" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -1520,7 +1520,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
     </row>
-    <row r="43" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43" s="5"/>
@@ -1533,12 +1533,12 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
     </row>
-    <row r="44" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C44" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -1550,12 +1550,12 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
     </row>
-    <row r="45" spans="3:13" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:13" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C45" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
@@ -1567,7 +1567,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
     </row>
-    <row r="46" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C46"/>
       <c r="D46"/>
       <c r="E46" s="5"/>
@@ -1580,12 +1580,12 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
     </row>
-    <row r="47" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C47" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -1597,12 +1597,12 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
     </row>
-    <row r="48" spans="3:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C48" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
@@ -1614,7 +1614,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.3">
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -1622,51 +1622,51 @@
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C50" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D50" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C51" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="51" spans="3:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="C51" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" s="16" t="s">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C53" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" s="15" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C53" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D53" s="15" t="s">
+      <c r="F53" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G53" s="15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C54" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F53" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="G53" s="15" t="s">
+      <c r="F54" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G54" s="16" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="3:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="C54" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -1676,12 +1676,12 @@
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
     </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C56" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
@@ -1690,12 +1690,12 @@
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
     </row>
-    <row r="57" spans="3:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C57" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
@@ -1704,7 +1704,7 @@
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
     </row>
-    <row r="58" spans="3:13" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:13" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
@@ -1714,12 +1714,12 @@
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C59" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F59" s="16" t="s">
         <v>0</v>
@@ -1746,15 +1746,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C60" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G60" s="16">
         <v>3</v>
@@ -1766,64 +1766,64 @@
         <v>26</v>
       </c>
       <c r="J60" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="K60" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="K60" s="16" t="s">
-        <v>73</v>
-      </c>
       <c r="L60" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M60" s="16">
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.3">
       <c r="F61" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="G61" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="H61" s="30"/>
-      <c r="I61" s="30"/>
-      <c r="J61" s="30"/>
-      <c r="K61" s="30"/>
-      <c r="L61" s="30"/>
-      <c r="M61" s="31"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="G61" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
+      <c r="J61" s="22"/>
+      <c r="K61" s="22"/>
+      <c r="L61" s="22"/>
+      <c r="M61" s="23"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.3">
       <c r="F62" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G62" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="H62" s="30"/>
-      <c r="I62" s="30"/>
-      <c r="J62" s="30"/>
-      <c r="K62" s="30"/>
-      <c r="L62" s="30"/>
-      <c r="M62" s="31"/>
+      <c r="G62" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="H62" s="22"/>
+      <c r="I62" s="22"/>
+      <c r="J62" s="22"/>
+      <c r="K62" s="22"/>
+      <c r="L62" s="22"/>
+      <c r="M62" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G15:M15"/>
+    <mergeCell ref="G16:M16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="F1:L1"/>
     <mergeCell ref="G61:M61"/>
     <mergeCell ref="G62:M62"/>
     <mergeCell ref="G23:M23"/>
     <mergeCell ref="G24:M24"/>
     <mergeCell ref="G38:M38"/>
     <mergeCell ref="G39:M39"/>
-    <mergeCell ref="G15:M15"/>
-    <mergeCell ref="G16:M16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="F1:L1"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1833,9 +1833,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1845,7 +1845,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/Items.xlsx
+++ b/Docs/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -171,9 +171,6 @@
     <t>Big green dice with sharp teeth and long tongue</t>
   </si>
   <si>
-    <t>Randomized</t>
-  </si>
-  <si>
     <t>Blood stew</t>
   </si>
   <si>
@@ -256,6 +253,9 @@
   </si>
   <si>
     <t>Vulnerable:Fire, Explosive (1), Unscoring</t>
+  </si>
+  <si>
+    <t>Randomized, Unscoring</t>
   </si>
 </sst>
 </file>
@@ -405,7 +405,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -467,16 +467,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
@@ -494,11 +497,29 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -806,43 +827,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M62"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="4"/>
+    <col min="1" max="1" width="8.85546875" style="4"/>
     <col min="2" max="2" width="5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="25.44140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="3.88671875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="46.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="40.44140625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="32.44140625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8.88671875" style="4"/>
-    <col min="13" max="13" width="5.109375" style="4" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="4"/>
+    <col min="3" max="3" width="7.85546875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="3.85546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="46.28515625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="40.42578125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="32.42578125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" style="4"/>
+    <col min="13" max="13" width="5.140625" style="4" customWidth="1"/>
+    <col min="14" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+    </row>
+    <row r="4" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -882,7 +903,7 @@
         <v>6</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H5"/>
       <c r="I5" s="7" t="s">
@@ -892,7 +913,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="46.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>34</v>
       </c>
@@ -901,7 +922,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -922,7 +943,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="6" t="s">
         <v>6</v>
       </c>
@@ -940,7 +961,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9" s="5"/>
@@ -950,7 +971,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C10" s="6" t="s">
         <v>0</v>
       </c>
@@ -962,25 +983,25 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
     </row>
-    <row r="11" spans="1:13" ht="28.95" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="28.9" x14ac:dyDescent="0.3">
       <c r="C11" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="E12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C13" s="6" t="s">
         <v>0</v>
       </c>
@@ -1013,11 +1034,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C14" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="29" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C14" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="30" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="5"/>
@@ -1037,49 +1058,49 @@
         <v>27</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M14" s="9">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C15" s="28"/>
-      <c r="D15" s="29"/>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C15" s="29"/>
+      <c r="D15" s="30"/>
       <c r="E15" s="5"/>
       <c r="F15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="27"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C16" s="28"/>
-      <c r="D16" s="29"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="28"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C16" s="29"/>
+      <c r="D16" s="30"/>
       <c r="F16" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="27"/>
-    </row>
-    <row r="17" spans="3:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="G16" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="28"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C17"/>
       <c r="D17"/>
       <c r="E17" s="5"/>
@@ -1114,7 +1135,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="3:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -1124,7 +1145,7 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
     </row>
-    <row r="21" spans="3:13" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:13" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="11" t="s">
         <v>0</v>
       </c>
@@ -1157,8 +1178,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="31" t="s">
+    <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="23" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="24" t="s">
@@ -1175,13 +1196,13 @@
         <v>0</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J22" s="12" t="s">
         <v>27</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L22" s="12" t="s">
         <v>47</v>
@@ -1190,8 +1211,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C23" s="31"/>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C23" s="23"/>
       <c r="D23" s="24"/>
       <c r="E23"/>
       <c r="F23" s="12" t="s">
@@ -1207,8 +1228,8 @@
       <c r="L23" s="24"/>
       <c r="M23" s="24"/>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C24" s="31"/>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C24" s="23"/>
       <c r="D24" s="24"/>
       <c r="E24"/>
       <c r="F24" s="12" t="s">
@@ -1224,7 +1245,7 @@
       <c r="L24" s="24"/>
       <c r="M24" s="24"/>
     </row>
-    <row r="25" spans="3:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -1234,11 +1255,11 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
     </row>
-    <row r="26" spans="3:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="C26" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D26" s="11" t="s">
+    <row r="26" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C26" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>39</v>
       </c>
       <c r="E26" s="5"/>
@@ -1248,12 +1269,12 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C27" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>78</v>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C27" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="38" t="s">
+        <v>77</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -1262,9 +1283,9 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C28" s="31"/>
-      <c r="D28" s="24"/>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C28" s="37"/>
+      <c r="D28" s="38"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -1272,9 +1293,9 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
     </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C29" s="31"/>
-      <c r="D29" s="24"/>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C29" s="37"/>
+      <c r="D29" s="38"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -1282,7 +1303,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
     </row>
-    <row r="30" spans="3:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
@@ -1292,7 +1313,7 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
     </row>
-    <row r="31" spans="3:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C31" s="18" t="s">
         <v>0</v>
       </c>
@@ -1313,7 +1334,7 @@
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
     </row>
-    <row r="32" spans="3:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:13" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="18" t="s">
         <v>6</v>
       </c>
@@ -1325,7 +1346,7 @@
         <v>6</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -1334,7 +1355,7 @@
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
     </row>
-    <row r="33" spans="3:13" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33"/>
@@ -1347,7 +1368,7 @@
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
     </row>
-    <row r="34" spans="3:13" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34"/>
@@ -1360,7 +1381,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
     </row>
-    <row r="35" spans="3:13" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -1373,107 +1394,107 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
     </row>
-    <row r="36" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D36" s="15" t="s">
+    <row r="36" spans="3:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D36" s="22" t="s">
         <v>44</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="G36" s="16" t="s">
+      <c r="F36" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="G36" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="H36" s="16" t="s">
+      <c r="H36" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="I36" s="16" t="s">
+      <c r="I36" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="J36" s="16" t="s">
+      <c r="J36" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="K36" s="16" t="s">
+      <c r="K36" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="L36" s="16" t="s">
+      <c r="L36" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="M36" s="16" t="s">
+      <c r="M36" s="21" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="37" spans="3:13" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="16" t="s">
+      <c r="C37" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="21" t="s">
         <v>48</v>
       </c>
       <c r="E37" s="5"/>
-      <c r="F37" s="16" t="s">
+      <c r="F37" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G37" s="16" t="s">
+      <c r="G37" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="H37" s="16" t="s">
+      <c r="H37" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="I37" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="J37" s="16" t="s">
+      <c r="I37" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="J37" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="K37" s="16" t="s">
+      <c r="K37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="L37" s="16" t="s">
+      <c r="L37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="M37" s="16">
+      <c r="M37" s="21">
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C38" s="15"/>
-      <c r="D38" s="16"/>
+    <row r="38" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C38" s="22"/>
+      <c r="D38" s="21"/>
       <c r="E38" s="5"/>
-      <c r="F38" s="16" t="s">
+      <c r="F38" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="G38" s="21" t="s">
+      <c r="G38" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="22"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="23"/>
-    </row>
-    <row r="39" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="15"/>
-      <c r="D39" s="16"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="35"/>
+      <c r="L38" s="35"/>
+      <c r="M38" s="36"/>
+    </row>
+    <row r="39" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C39" s="22"/>
+      <c r="D39" s="21"/>
       <c r="E39" s="5"/>
-      <c r="F39" s="16" t="s">
+      <c r="F39" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="G39" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="22"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="23"/>
-    </row>
-    <row r="40" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G39" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
+      <c r="J39" s="35"/>
+      <c r="K39" s="35"/>
+      <c r="L39" s="35"/>
+      <c r="M39" s="36"/>
+    </row>
+    <row r="40" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -1486,12 +1507,12 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
     </row>
-    <row r="41" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>52</v>
+    <row r="41" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="22" t="s">
+        <v>51</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -1503,12 +1524,12 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
     </row>
-    <row r="42" spans="3:13" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>53</v>
+    <row r="42" spans="3:13" ht="50.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>52</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -1520,7 +1541,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
     </row>
-    <row r="43" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43" s="5"/>
@@ -1533,12 +1554,12 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
     </row>
-    <row r="44" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C44" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -1550,12 +1571,12 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
     </row>
-    <row r="45" spans="3:13" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:13" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
@@ -1567,7 +1588,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
     </row>
-    <row r="46" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46"/>
       <c r="D46"/>
       <c r="E46" s="5"/>
@@ -1580,12 +1601,12 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
     </row>
-    <row r="47" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -1597,12 +1618,12 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
     </row>
-    <row r="48" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:13" ht="30" x14ac:dyDescent="0.25">
       <c r="C48" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
@@ -1614,7 +1635,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -1622,51 +1643,51 @@
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C50" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D50" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="C51" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="16" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="3:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="C51" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" s="16" t="s">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C53" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" s="15" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C53" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D53" s="15" t="s">
+      <c r="F53" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G53" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="C54" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F53" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="G53" s="15" t="s">
+      <c r="F54" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G54" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="54" spans="3:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="C54" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -1676,12 +1697,12 @@
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
     </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C56" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
@@ -1690,12 +1711,12 @@
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
     </row>
-    <row r="57" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:13" ht="30" x14ac:dyDescent="0.25">
       <c r="C57" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
@@ -1704,7 +1725,7 @@
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
     </row>
-    <row r="58" spans="3:13" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:13" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
@@ -1714,12 +1735,12 @@
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C59" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F59" s="16" t="s">
         <v>0</v>
@@ -1746,15 +1767,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C60" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G60" s="16">
         <v>3</v>
@@ -1766,64 +1787,64 @@
         <v>26</v>
       </c>
       <c r="J60" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="K60" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="K60" s="16" t="s">
-        <v>72</v>
-      </c>
       <c r="L60" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M60" s="16">
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.25">
       <c r="F61" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="G61" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="H61" s="22"/>
-      <c r="I61" s="22"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="23"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="G61" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="32"/>
+      <c r="L61" s="32"/>
+      <c r="M61" s="33"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.25">
       <c r="F62" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G62" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="H62" s="22"/>
-      <c r="I62" s="22"/>
-      <c r="J62" s="22"/>
-      <c r="K62" s="22"/>
-      <c r="L62" s="22"/>
-      <c r="M62" s="23"/>
+      <c r="G62" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="H62" s="32"/>
+      <c r="I62" s="32"/>
+      <c r="J62" s="32"/>
+      <c r="K62" s="32"/>
+      <c r="L62" s="32"/>
+      <c r="M62" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G15:M15"/>
-    <mergeCell ref="G16:M16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="F1:L1"/>
     <mergeCell ref="G61:M61"/>
     <mergeCell ref="G62:M62"/>
     <mergeCell ref="G23:M23"/>
     <mergeCell ref="G24:M24"/>
     <mergeCell ref="G38:M38"/>
     <mergeCell ref="G39:M39"/>
+    <mergeCell ref="G15:M15"/>
+    <mergeCell ref="G16:M16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="F1:L1"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1833,9 +1854,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1845,7 +1866,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/Items.xlsx
+++ b/Docs/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="82">
   <si>
     <t>Name</t>
   </si>
@@ -153,9 +153,6 @@
     <t>A critical roll</t>
   </si>
   <si>
-    <t>D6</t>
-  </si>
-  <si>
     <t>D2</t>
   </si>
   <si>
@@ -177,9 +174,6 @@
     <t>Selected unit gains "Strengthened" and "Exposed"</t>
   </si>
   <si>
-    <t>D4                                                                           (Physical, Fire, Lightning, Frost)</t>
-  </si>
-  <si>
     <t>Polymorph hex</t>
   </si>
   <si>
@@ -192,12 +186,6 @@
     <t>Applies "Exposed" to selected unit</t>
   </si>
   <si>
-    <t>Crystal of blood</t>
-  </si>
-  <si>
-    <t>Applies "Bloodthirsty" to all units in a 3x3 square</t>
-  </si>
-  <si>
     <t>Mida's paw</t>
   </si>
   <si>
@@ -256,6 +244,24 @@
   </si>
   <si>
     <t>Randomized, Unscoring</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>Crystal of bloodlust</t>
+  </si>
+  <si>
+    <t>Covers 1 cell in "Blood vapor"</t>
+  </si>
+  <si>
+    <t>Blood vapor</t>
+  </si>
+  <si>
+    <t>Applies "Bloodthirsty" to all units on top</t>
+  </si>
+  <si>
+    <t>D4                                                                         (Physical, Fire, Lightning, Frost)</t>
   </si>
 </sst>
 </file>
@@ -437,46 +443,52 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -513,12 +525,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -846,22 +852,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
     </row>
     <row r="4" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -902,14 +908,14 @@
       <c r="F5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="20" t="s">
-        <v>76</v>
+      <c r="G5" s="18" t="s">
+        <v>72</v>
       </c>
       <c r="H5"/>
       <c r="I5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="11" t="s">
         <v>11</v>
       </c>
     </row>
@@ -988,7 +994,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E11" s="5"/>
       <c r="H11" s="5"/>
@@ -1035,10 +1041,10 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C14" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="30" t="s">
+      <c r="C14" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="32" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="5"/>
@@ -1058,47 +1064,47 @@
         <v>27</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="M14" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="29"/>
-      <c r="D15" s="30"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="32"/>
       <c r="E15" s="5"/>
       <c r="F15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="G15" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="28"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="30"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="29"/>
-      <c r="D16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="32"/>
       <c r="F16" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="28"/>
+      <c r="G16" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="30"/>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C17"/>
@@ -1146,104 +1152,104 @@
       <c r="J20" s="5"/>
     </row>
     <row r="21" spans="3:13" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="11" t="s">
+      <c r="C21" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="23" t="s">
         <v>35</v>
       </c>
       <c r="E21"/>
-      <c r="F21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="12" t="s">
+      <c r="F21" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="K21" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="L21" s="12" t="s">
+      <c r="L21" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="M21" s="12" t="s">
+      <c r="M21" s="24" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="24" t="s">
+      <c r="C22" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="26" t="s">
         <v>36</v>
       </c>
       <c r="E22"/>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="24">
         <v>3</v>
       </c>
-      <c r="H22" s="12">
-        <v>0</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="J22" s="12" t="s">
+      <c r="H22" s="24">
+        <v>0</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="J22" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="K22" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="M22" s="12">
+      <c r="K22" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="L22" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="M22" s="24">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C23" s="23"/>
-      <c r="D23" s="24"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="26"/>
       <c r="E23"/>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="24" t="s">
+      <c r="G23" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
     </row>
     <row r="24" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C24" s="23"/>
-      <c r="D24" s="24"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="26"/>
       <c r="E24"/>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="24" t="s">
+      <c r="G24" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
     </row>
     <row r="25" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C25" s="5"/>
@@ -1270,11 +1276,11 @@
       <c r="J26" s="5"/>
     </row>
     <row r="27" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C27" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>77</v>
+      <c r="C27" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>73</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -1284,8 +1290,8 @@
       <c r="J27" s="5"/>
     </row>
     <row r="28" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C28" s="37"/>
-      <c r="D28" s="38"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="26"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -1294,8 +1300,8 @@
       <c r="J28" s="5"/>
     </row>
     <row r="29" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C29" s="37"/>
-      <c r="D29" s="38"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="26"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -1314,46 +1320,46 @@
       <c r="J30" s="5"/>
     </row>
     <row r="31" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C31" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D31" s="18" t="s">
+      <c r="C31" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="16" t="s">
         <v>41</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="G31" s="18" t="s">
+      <c r="F31" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" s="16" t="s">
         <v>42</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
     </row>
     <row r="32" spans="3:13" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="19" t="s">
+      <c r="C32" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="17" t="s">
         <v>43</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>56</v>
+      <c r="F32" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>54</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
     </row>
     <row r="33" spans="3:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33"/>
@@ -1364,9 +1370,9 @@
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
     </row>
     <row r="34" spans="3:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34"/>
@@ -1377,9 +1383,9 @@
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
     </row>
     <row r="35" spans="3:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="5"/>
@@ -1390,109 +1396,109 @@
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
     </row>
     <row r="36" spans="3:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D36" s="22" t="s">
+      <c r="C36" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D36" s="20" t="s">
         <v>44</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="G36" s="21" t="s">
+      <c r="F36" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="G36" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="H36" s="21" t="s">
+      <c r="H36" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="I36" s="21" t="s">
+      <c r="I36" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="J36" s="21" t="s">
+      <c r="J36" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="K36" s="21" t="s">
+      <c r="K36" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="L36" s="21" t="s">
+      <c r="L36" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="M36" s="21" t="s">
+      <c r="M36" s="19" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="37" spans="3:13" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="21" t="s">
+      <c r="C37" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E37" s="5"/>
+      <c r="F37" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="21" t="s">
+      <c r="G37" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="H37" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I37" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="J37" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K37" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="L37" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="M37" s="19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C38" s="20"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G38" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="G37" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="H37" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="I37" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="J37" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="K37" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="L37" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="M37" s="21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C38" s="22"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="G38" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35"/>
-      <c r="J38" s="35"/>
-      <c r="K38" s="35"/>
-      <c r="L38" s="35"/>
-      <c r="M38" s="36"/>
+      <c r="H38" s="37"/>
+      <c r="I38" s="37"/>
+      <c r="J38" s="37"/>
+      <c r="K38" s="37"/>
+      <c r="L38" s="37"/>
+      <c r="M38" s="38"/>
     </row>
     <row r="39" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C39" s="22"/>
-      <c r="D39" s="21"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="19"/>
       <c r="E39" s="5"/>
-      <c r="F39" s="21" t="s">
+      <c r="F39" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="G39" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="H39" s="35"/>
-      <c r="I39" s="35"/>
-      <c r="J39" s="35"/>
-      <c r="K39" s="35"/>
-      <c r="L39" s="35"/>
-      <c r="M39" s="36"/>
+      <c r="G39" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="H39" s="37"/>
+      <c r="I39" s="37"/>
+      <c r="J39" s="37"/>
+      <c r="K39" s="37"/>
+      <c r="L39" s="37"/>
+      <c r="M39" s="38"/>
     </row>
     <row r="40" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="5"/>
@@ -1503,16 +1509,16 @@
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
     </row>
     <row r="41" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>51</v>
+      <c r="C41" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>50</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -1520,16 +1526,16 @@
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
     </row>
     <row r="42" spans="3:13" ht="50.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="21" t="s">
-        <v>52</v>
+      <c r="C42" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>51</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -1537,9 +1543,9 @@
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
+      <c r="M42" s="15"/>
     </row>
     <row r="43" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C43"/>
@@ -1550,16 +1556,16 @@
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
+      <c r="K43" s="15"/>
+      <c r="L43" s="15"/>
+      <c r="M43" s="15"/>
     </row>
     <row r="44" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C44" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>54</v>
+      <c r="C44" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -1567,16 +1573,16 @@
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="15"/>
     </row>
     <row r="45" spans="3:13" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>55</v>
+      <c r="C45" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
@@ -1584,9 +1590,9 @@
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
+      <c r="M45" s="15"/>
     </row>
     <row r="46" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46"/>
@@ -1597,43 +1603,51 @@
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="15"/>
+      <c r="M46" s="15"/>
     </row>
     <row r="47" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>58</v>
+      <c r="C47" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>77</v>
       </c>
       <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
+      <c r="F47" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>79</v>
+      </c>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-      <c r="M47" s="17"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="15"/>
     </row>
     <row r="48" spans="3:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="C48" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>59</v>
+      <c r="C48" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="22" t="s">
+        <v>78</v>
       </c>
       <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
+      <c r="F48" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="G48" s="22" t="s">
+        <v>80</v>
+      </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="15"/>
     </row>
     <row r="49" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E49" s="5"/>
@@ -1644,47 +1658,47 @@
       <c r="J49" s="5"/>
     </row>
     <row r="50" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C50" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D50" s="15" t="s">
+      <c r="C50" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="C51" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C53" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F53" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G53" s="13" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="3:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="C51" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" s="16" t="s">
+    <row r="54" spans="3:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="C54" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F54" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G54" s="14" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C53" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="G53" s="15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="54" spans="3:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="C54" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.25">
@@ -1698,11 +1712,11 @@
       <c r="J55" s="5"/>
     </row>
     <row r="56" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C56" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>66</v>
+      <c r="C56" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
@@ -1712,11 +1726,11 @@
       <c r="J56" s="5"/>
     </row>
     <row r="57" spans="3:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="C57" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>67</v>
+      <c r="C57" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>63</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
@@ -1736,96 +1750,96 @@
       <c r="J58" s="5"/>
     </row>
     <row r="59" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C59" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="F59" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="G59" s="16" t="s">
+      <c r="C59" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F59" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H59" s="16" t="s">
+      <c r="H59" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="I59" s="16" t="s">
+      <c r="I59" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J59" s="16" t="s">
+      <c r="J59" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="K59" s="16" t="s">
+      <c r="K59" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="L59" s="16" t="s">
+      <c r="L59" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="M59" s="16" t="s">
+      <c r="M59" s="14" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="60" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C60" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D60" s="16" t="s">
+      <c r="C60" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F60" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G60" s="14">
+        <v>3</v>
+      </c>
+      <c r="H60" s="14">
+        <v>0</v>
+      </c>
+      <c r="I60" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="J60" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="K60" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L60" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="M60" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="F61" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G61" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="H61" s="34"/>
+      <c r="I61" s="34"/>
+      <c r="J61" s="34"/>
+      <c r="K61" s="34"/>
+      <c r="L61" s="34"/>
+      <c r="M61" s="35"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="F62" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="F60" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G60" s="16">
-        <v>3</v>
-      </c>
-      <c r="H60" s="16">
-        <v>0</v>
-      </c>
-      <c r="I60" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="J60" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="K60" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="L60" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="M60" s="16">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="F61" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="G61" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="H61" s="32"/>
-      <c r="I61" s="32"/>
-      <c r="J61" s="32"/>
-      <c r="K61" s="32"/>
-      <c r="L61" s="32"/>
-      <c r="M61" s="33"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="F62" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="G62" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="H62" s="32"/>
-      <c r="I62" s="32"/>
-      <c r="J62" s="32"/>
-      <c r="K62" s="32"/>
-      <c r="L62" s="32"/>
-      <c r="M62" s="33"/>
+      <c r="H62" s="34"/>
+      <c r="I62" s="34"/>
+      <c r="J62" s="34"/>
+      <c r="K62" s="34"/>
+      <c r="L62" s="34"/>
+      <c r="M62" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/Docs/Items.xlsx
+++ b/Docs/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="84">
   <si>
     <t>Name</t>
   </si>
@@ -180,9 +180,6 @@
     <t>Applies "Polymorphed" to selected unit</t>
   </si>
   <si>
-    <t>At the end of the round, deals 3 (Lightning) damage to units on top</t>
-  </si>
-  <si>
     <t>Applies "Exposed" to selected unit</t>
   </si>
   <si>
@@ -262,6 +259,15 @@
   </si>
   <si>
     <t>D4                                                                         (Physical, Fire, Lightning, Frost)</t>
+  </si>
+  <si>
+    <t>Polymorphed animal</t>
+  </si>
+  <si>
+    <t>A rabbit, sheep or a big sheep depending on the size</t>
+  </si>
+  <si>
+    <t>At the end of the round, deals 2 (Lightning) damage to units on top</t>
   </si>
 </sst>
 </file>
@@ -458,22 +464,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
@@ -491,7 +491,25 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
@@ -509,23 +527,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -832,7 +838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="4"/>
@@ -852,22 +858,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
     </row>
     <row r="4" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -908,8 +914,8 @@
       <c r="F5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="18" t="s">
-        <v>72</v>
+      <c r="G5" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="H5"/>
       <c r="I5" s="7" t="s">
@@ -994,7 +1000,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" s="5"/>
       <c r="H11" s="5"/>
@@ -1041,10 +1047,10 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C14" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="32" t="s">
+      <c r="C14" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="36" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="5"/>
@@ -1064,47 +1070,47 @@
         <v>27</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M14" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="31"/>
-      <c r="D15" s="32"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="36"/>
       <c r="E15" s="5"/>
       <c r="F15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="28" t="s">
+      <c r="G15" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="30"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="34"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="31"/>
-      <c r="D16" s="32"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="36"/>
       <c r="F16" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="30"/>
+      <c r="G16" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="34"/>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C17"/>
@@ -1152,104 +1158,104 @@
       <c r="J20" s="5"/>
     </row>
     <row r="21" spans="3:13" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="23" t="s">
+      <c r="C21" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="21" t="s">
         <v>35</v>
       </c>
       <c r="E21"/>
-      <c r="F21" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="24" t="s">
+      <c r="F21" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="H21" s="24" t="s">
+      <c r="H21" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="24" t="s">
+      <c r="I21" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="J21" s="24" t="s">
+      <c r="J21" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="K21" s="24" t="s">
+      <c r="K21" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="L21" s="24" t="s">
+      <c r="L21" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="M21" s="24" t="s">
+      <c r="M21" s="22" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="26" t="s">
+      <c r="C22" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="28" t="s">
         <v>36</v>
       </c>
       <c r="E22"/>
-      <c r="F22" s="24" t="s">
+      <c r="F22" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="22">
         <v>3</v>
       </c>
-      <c r="H22" s="24">
-        <v>0</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="J22" s="24" t="s">
+      <c r="H22" s="22">
+        <v>0</v>
+      </c>
+      <c r="I22" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="J22" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="K22" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="L22" s="24" t="s">
+      <c r="K22" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="L22" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="M22" s="24">
+      <c r="M22" s="22">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C23" s="25"/>
-      <c r="D23" s="26"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="28"/>
       <c r="E23"/>
-      <c r="F23" s="24" t="s">
+      <c r="F23" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
     </row>
     <row r="24" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C24" s="25"/>
-      <c r="D24" s="26"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="28"/>
       <c r="E24"/>
-      <c r="F24" s="24" t="s">
+      <c r="F24" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="26" t="s">
+      <c r="G24" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="28"/>
     </row>
     <row r="25" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C25" s="5"/>
@@ -1276,11 +1282,11 @@
       <c r="J26" s="5"/>
     </row>
     <row r="27" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C27" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>73</v>
+      <c r="C27" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>72</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -1290,8 +1296,8 @@
       <c r="J27" s="5"/>
     </row>
     <row r="28" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C28" s="25"/>
-      <c r="D28" s="26"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="28"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -1300,8 +1306,8 @@
       <c r="J28" s="5"/>
     </row>
     <row r="29" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C29" s="25"/>
-      <c r="D29" s="26"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="28"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -1320,17 +1326,17 @@
       <c r="J30" s="5"/>
     </row>
     <row r="31" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C31" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D31" s="16" t="s">
+      <c r="C31" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="23" t="s">
         <v>41</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="G31" s="16" t="s">
+      <c r="F31" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" s="23" t="s">
         <v>42</v>
       </c>
       <c r="H31" s="5"/>
@@ -1341,18 +1347,18 @@
       <c r="M31" s="12"/>
     </row>
     <row r="32" spans="3:13" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="17" t="s">
+      <c r="C32" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="24" t="s">
         <v>43</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G32" s="17" t="s">
-        <v>54</v>
+      <c r="F32" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" s="24" t="s">
+        <v>83</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -1401,104 +1407,104 @@
       <c r="M35" s="15"/>
     </row>
     <row r="36" spans="3:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D36" s="20" t="s">
+      <c r="C36" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D36" s="23" t="s">
         <v>44</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="G36" s="19" t="s">
+      <c r="F36" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="G36" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="H36" s="19" t="s">
+      <c r="H36" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="I36" s="19" t="s">
+      <c r="I36" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J36" s="19" t="s">
+      <c r="J36" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="K36" s="19" t="s">
+      <c r="K36" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="L36" s="19" t="s">
+      <c r="L36" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="M36" s="19" t="s">
+      <c r="M36" s="24" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="37" spans="3:13" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="19" t="s">
+      <c r="C37" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="24" t="s">
         <v>47</v>
       </c>
       <c r="E37" s="5"/>
-      <c r="F37" s="19" t="s">
+      <c r="F37" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="G37" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="H37" s="19" t="s">
+      <c r="G37" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="H37" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="I37" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="J37" s="19" t="s">
+      <c r="I37" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="J37" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="K37" s="19" t="s">
+      <c r="K37" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L37" s="19" t="s">
+      <c r="L37" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="M37" s="19">
+      <c r="M37" s="24">
         <v>20</v>
       </c>
     </row>
     <row r="38" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C38" s="20"/>
-      <c r="D38" s="19"/>
+      <c r="C38"/>
+      <c r="D38"/>
       <c r="E38" s="5"/>
-      <c r="F38" s="19" t="s">
+      <c r="F38" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="G38" s="36" t="s">
+      <c r="G38" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="H38" s="37"/>
-      <c r="I38" s="37"/>
-      <c r="J38" s="37"/>
-      <c r="K38" s="37"/>
-      <c r="L38" s="37"/>
-      <c r="M38" s="38"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="33"/>
+      <c r="L38" s="33"/>
+      <c r="M38" s="34"/>
     </row>
     <row r="39" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C39" s="20"/>
-      <c r="D39" s="19"/>
+      <c r="C39"/>
+      <c r="D39"/>
       <c r="E39" s="5"/>
-      <c r="F39" s="19" t="s">
+      <c r="F39" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="G39" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="H39" s="37"/>
-      <c r="I39" s="37"/>
-      <c r="J39" s="37"/>
-      <c r="K39" s="37"/>
-      <c r="L39" s="37"/>
-      <c r="M39" s="38"/>
+      <c r="G39" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="34"/>
     </row>
     <row r="40" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="5"/>
@@ -1514,10 +1520,10 @@
       <c r="M40" s="15"/>
     </row>
     <row r="41" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="20" t="s">
+      <c r="C41" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="18" t="s">
         <v>50</v>
       </c>
       <c r="E41" s="5"/>
@@ -1531,10 +1537,10 @@
       <c r="M41" s="15"/>
     </row>
     <row r="42" spans="3:13" ht="50.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="19" t="s">
+      <c r="C42" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="17" t="s">
         <v>51</v>
       </c>
       <c r="E42" s="5"/>
@@ -1561,177 +1567,194 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C44" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D44" s="13" t="s">
+      <c r="C44" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D44" s="19" t="s">
         <v>52</v>
       </c>
       <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
-      <c r="M44" s="15"/>
+      <c r="F44" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="G44" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K44" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="M44" s="20" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="45" spans="3:13" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="14" t="s">
+      <c r="C45" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="20" t="s">
         <v>53</v>
       </c>
       <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
-      <c r="M45" s="15"/>
+      <c r="F45" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G45" s="20">
+        <v>2</v>
+      </c>
+      <c r="H45" s="20">
+        <v>0</v>
+      </c>
+      <c r="I45" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J45" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="K45" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="L45" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M45" s="20">
+        <v>10</v>
+      </c>
     </row>
     <row r="46" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46"/>
       <c r="D46"/>
       <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-      <c r="M46" s="15"/>
+      <c r="F46" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G46" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="31"/>
     </row>
     <row r="47" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="D47" s="21" t="s">
+      <c r="F47" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="31"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C49" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D49" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E49" s="5"/>
+      <c r="F49" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="G49" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="H49" s="5"/>
+    </row>
+    <row r="50" spans="3:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="C50" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="G47" s="21" t="s">
+      <c r="E50" s="5"/>
+      <c r="F50" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="G50" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-      <c r="M47" s="15"/>
-    </row>
-    <row r="48" spans="3:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="C48" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G48" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C50" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D50" s="13" t="s">
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="15"/>
+      <c r="L50" s="15"/>
+      <c r="M50" s="15"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C52" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="C53" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="14" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="3:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="C51" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" s="14" t="s">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C55" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D55" s="13" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C53" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D53" s="13" t="s">
+      <c r="F55" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G55" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="56" spans="3:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="C56" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="F53" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="G53" s="13" t="s">
+      <c r="F56" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G56" s="14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="3:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="C54" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="G54" s="14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C56" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
-    </row>
-    <row r="57" spans="3:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="C57" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>63</v>
-      </c>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -1740,8 +1763,12 @@
       <c r="J57" s="5"/>
     </row>
     <row r="58" spans="3:13" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
+      <c r="C58" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>61</v>
+      </c>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -1749,116 +1776,142 @@
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C59" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F59" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G59" s="14" t="s">
+    <row r="59" spans="3:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="C59" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C61" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F61" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H59" s="14" t="s">
+      <c r="H61" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="I59" s="14" t="s">
+      <c r="I61" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J59" s="14" t="s">
+      <c r="J61" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="K59" s="14" t="s">
+      <c r="K61" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="L59" s="14" t="s">
+      <c r="L61" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="M59" s="14" t="s">
+      <c r="M61" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C60" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D60" s="14" t="s">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C62" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F62" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G62" s="14">
+        <v>3</v>
+      </c>
+      <c r="H62" s="14">
+        <v>0</v>
+      </c>
+      <c r="I62" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="J62" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="F60" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="G60" s="14">
-        <v>3</v>
-      </c>
-      <c r="H60" s="14">
-        <v>0</v>
-      </c>
-      <c r="I60" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="J60" s="14" t="s">
+      <c r="K62" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="K60" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="L60" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="M60" s="14">
+      <c r="L62" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="M62" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="F61" s="14" t="s">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="F63" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G61" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="H61" s="34"/>
-      <c r="I61" s="34"/>
-      <c r="J61" s="34"/>
-      <c r="K61" s="34"/>
-      <c r="L61" s="34"/>
-      <c r="M61" s="35"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="F62" s="14" t="s">
+      <c r="G63" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="H63" s="26"/>
+      <c r="I63" s="26"/>
+      <c r="J63" s="26"/>
+      <c r="K63" s="26"/>
+      <c r="L63" s="26"/>
+      <c r="M63" s="27"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="F64" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="G62" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="H62" s="34"/>
-      <c r="I62" s="34"/>
-      <c r="J62" s="34"/>
-      <c r="K62" s="34"/>
-      <c r="L62" s="34"/>
-      <c r="M62" s="35"/>
+      <c r="G64" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="H64" s="26"/>
+      <c r="I64" s="26"/>
+      <c r="J64" s="26"/>
+      <c r="K64" s="26"/>
+      <c r="L64" s="26"/>
+      <c r="M64" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="G61:M61"/>
-    <mergeCell ref="G62:M62"/>
-    <mergeCell ref="G23:M23"/>
-    <mergeCell ref="G24:M24"/>
-    <mergeCell ref="G38:M38"/>
-    <mergeCell ref="G39:M39"/>
+  <mergeCells count="18">
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="G15:M15"/>
     <mergeCell ref="G16:M16"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="D14:D16"/>
     <mergeCell ref="F1:L1"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G63:M63"/>
+    <mergeCell ref="G64:M64"/>
+    <mergeCell ref="G23:M23"/>
+    <mergeCell ref="G24:M24"/>
+    <mergeCell ref="G38:M38"/>
+    <mergeCell ref="G39:M39"/>
+    <mergeCell ref="G46:M46"/>
+    <mergeCell ref="G47:M47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Docs/Items.xlsx
+++ b/Docs/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="88">
   <si>
     <t>Name</t>
   </si>
@@ -268,6 +268,18 @@
   </si>
   <si>
     <t>At the end of the round, deals 2 (Lightning) damage to units on top</t>
+  </si>
+  <si>
+    <t>Graveyard</t>
+  </si>
+  <si>
+    <t>Cover a 3x3 square in Graveyard</t>
+  </si>
+  <si>
+    <t>Units within gain "Undead"</t>
+  </si>
+  <si>
+    <t>Shovel</t>
   </si>
 </sst>
 </file>
@@ -503,6 +515,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -510,15 +531,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
@@ -838,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="4"/>
@@ -1086,15 +1098,15 @@
       <c r="F15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="34"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="31"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C16" s="35"/>
@@ -1102,15 +1114,15 @@
       <c r="F16" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="34"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="31"/>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C17"/>
@@ -1479,15 +1491,15 @@
       <c r="F38" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="G38" s="32" t="s">
+      <c r="G38" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="33"/>
-      <c r="L38" s="33"/>
-      <c r="M38" s="34"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="31"/>
     </row>
     <row r="39" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C39"/>
@@ -1496,15 +1508,15 @@
       <c r="F39" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="G39" s="32" t="s">
+      <c r="G39" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
-      <c r="L39" s="33"/>
-      <c r="M39" s="34"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="31"/>
     </row>
     <row r="40" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="5"/>
@@ -1639,29 +1651,29 @@
       <c r="F46" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G46" s="29" t="s">
+      <c r="G46" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="31"/>
+      <c r="H46" s="33"/>
+      <c r="I46" s="33"/>
+      <c r="J46" s="33"/>
+      <c r="K46" s="33"/>
+      <c r="L46" s="33"/>
+      <c r="M46" s="34"/>
     </row>
     <row r="47" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F47" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="G47" s="29" t="s">
+      <c r="G47" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="H47" s="30"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="30"/>
-      <c r="K47" s="30"/>
-      <c r="L47" s="30"/>
-      <c r="M47" s="31"/>
+      <c r="H47" s="33"/>
+      <c r="I47" s="33"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="33"/>
+      <c r="M47" s="34"/>
     </row>
     <row r="49" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C49" s="23" t="s">
@@ -1725,30 +1737,30 @@
       </c>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C55" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D55" s="13" t="s">
+      <c r="C55" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D55" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F55" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="G55" s="13" t="s">
+      <c r="F55" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="G55" s="19" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="56" spans="3:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="C56" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D56" s="14" t="s">
+      <c r="C56" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="F56" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="G56" s="14" t="s">
+      <c r="F56" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G56" s="20" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1891,6 +1903,34 @@
       <c r="K64" s="26"/>
       <c r="L64" s="26"/>
       <c r="M64" s="27"/>
+    </row>
+    <row r="66" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C66" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F66" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G66" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="67" spans="3:7" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C67" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" s="14" t="s">
+        <v>86</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/Docs/Items.xlsx
+++ b/Docs/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="90">
   <si>
     <t>Name</t>
   </si>
@@ -171,9 +171,6 @@
     <t>Blood stew</t>
   </si>
   <si>
-    <t>Selected unit gains "Strengthened" and "Exposed"</t>
-  </si>
-  <si>
     <t>Polymorph hex</t>
   </si>
   <si>
@@ -280,6 +277,15 @@
   </si>
   <si>
     <t>Shovel</t>
+  </si>
+  <si>
+    <t>Selected unit gains "Lethal" and "Exposed"</t>
+  </si>
+  <si>
+    <t>Ice bucket</t>
+  </si>
+  <si>
+    <t>Covers 3x3 square in Ice</t>
   </si>
 </sst>
 </file>
@@ -429,7 +435,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -449,48 +455,42 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -498,21 +498,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
@@ -522,15 +528,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
@@ -539,11 +536,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -850,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="4"/>
@@ -869,25 +869,25 @@
     <col min="14" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:12" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="A1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-    </row>
-    <row r="4" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -898,21 +898,15 @@
         <v>7</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="F4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="5"/>
-      <c r="I4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:12" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -923,22 +917,16 @@
         <v>8</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>71</v>
+      <c r="F5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>70</v>
       </c>
       <c r="H5"/>
-      <c r="I5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="46.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+    </row>
+    <row r="6" spans="1:12" ht="46.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
         <v>34</v>
       </c>
       <c r="E6" s="5"/>
@@ -946,380 +934,361 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:13" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="C7" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C11" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8" t="s">
+      <c r="E11" s="5"/>
+      <c r="F11" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-    </row>
-    <row r="8" spans="1:13" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-    </row>
-    <row r="9" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9" s="5"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-    </row>
-    <row r="10" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="C10" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-    </row>
-    <row r="11" spans="1:13" ht="28.9" x14ac:dyDescent="0.3">
-      <c r="C11" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="E12" s="5"/>
+      <c r="F12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="C13" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="6" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13" s="5"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C14" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="C15" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C17" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G13" s="9" t="s">
+      <c r="E17" s="5"/>
+      <c r="F17" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I17" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J17" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="K17" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L17" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="M17" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C14" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="36" t="s">
+    <row r="18" spans="3:13" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="33" t="s">
         <v>18</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="9">
-        <v>2</v>
-      </c>
-      <c r="H14" s="9">
-        <v>0</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="M14" s="9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="35"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="31"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="35"/>
-      <c r="D16" s="36"/>
-      <c r="F16" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="G16" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="31"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C17"/>
-      <c r="D17"/>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="3:13" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="3:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="C19" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>31</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="G18" s="8">
+        <v>2</v>
+      </c>
+      <c r="H18" s="8">
+        <v>0</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M18" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C19" s="32"/>
+      <c r="D19" s="33"/>
       <c r="E19" s="5"/>
       <c r="F19" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="31"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C20" s="32"/>
+      <c r="D20" s="33"/>
+      <c r="F20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="31"/>
+    </row>
+    <row r="21" spans="3:13" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="C23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-    </row>
-    <row r="21" spans="3:13" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="21" t="s">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C25" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D25" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E21"/>
-      <c r="F21" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="22" t="s">
+      <c r="E25"/>
+      <c r="F25" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H21" s="22" t="s">
+      <c r="H25" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="22" t="s">
+      <c r="I25" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="J21" s="22" t="s">
+      <c r="J25" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="K21" s="22" t="s">
+      <c r="K25" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="L21" s="22" t="s">
+      <c r="L25" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M21" s="22" t="s">
+      <c r="M25" s="18" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="28" t="s">
+    <row r="26" spans="3:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="C26" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="E22"/>
-      <c r="F22" s="22" t="s">
+      <c r="E26"/>
+      <c r="F26" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G26" s="18">
         <v>3</v>
       </c>
-      <c r="H22" s="22">
-        <v>0</v>
-      </c>
-      <c r="I22" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="J22" s="22" t="s">
+      <c r="H26" s="18">
+        <v>0</v>
+      </c>
+      <c r="I26" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="J26" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="K22" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="L22" s="22" t="s">
+      <c r="K26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="L26" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="M22" s="22">
+      <c r="M26" s="18">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C23" s="38"/>
-      <c r="D23" s="28"/>
-      <c r="E23"/>
-      <c r="F23" s="22" t="s">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C27" s="26"/>
+      <c r="D27" s="27"/>
+      <c r="E27"/>
+      <c r="F27" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="28" t="s">
+      <c r="G27" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C24" s="38"/>
-      <c r="D24" s="28"/>
-      <c r="E24"/>
-      <c r="F24" s="22" t="s">
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C28" s="26"/>
+      <c r="D28" s="27"/>
+      <c r="E28"/>
+      <c r="F28" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="28" t="s">
+      <c r="G28" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="28"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C26" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C27" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C28" s="38"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
     </row>
     <row r="29" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C29" s="38"/>
-      <c r="D29" s="28"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -1328,8 +1297,12 @@
       <c r="J29" s="5"/>
     </row>
     <row r="30" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -1338,620 +1311,673 @@
       <c r="J30" s="5"/>
     </row>
     <row r="31" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C31" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>41</v>
+      <c r="C31" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>71</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="G31" s="23" t="s">
-        <v>42</v>
-      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
     </row>
     <row r="32" spans="3:13" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="24" t="s">
-        <v>43</v>
-      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
       <c r="E32" s="5"/>
-      <c r="F32" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="G32" s="24" t="s">
-        <v>83</v>
-      </c>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
     </row>
     <row r="33" spans="3:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33"/>
-      <c r="D33"/>
-      <c r="E33"/>
-      <c r="F33"/>
-      <c r="G33"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
     </row>
     <row r="34" spans="3:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34"/>
-      <c r="D34"/>
-      <c r="E34"/>
-      <c r="F34"/>
-      <c r="G34"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
     </row>
     <row r="35" spans="3:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
+      <c r="C35" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>41</v>
+      </c>
       <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
+      <c r="F35" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>42</v>
+      </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
     </row>
     <row r="36" spans="3:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>44</v>
+      <c r="C36" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>43</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="G36" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="I36" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J36" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="K36" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="L36" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M36" s="24" t="s">
-        <v>25</v>
-      </c>
+      <c r="F36" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
     </row>
     <row r="37" spans="3:13" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="G37" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="H37" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="I37" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="J37" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="K37" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L37" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M37" s="24">
-        <v>20</v>
-      </c>
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
     </row>
     <row r="38" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C38"/>
       <c r="D38"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="24" t="s">
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+    </row>
+    <row r="39" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+    </row>
+    <row r="40" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="5"/>
+      <c r="F40" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="I40" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K40" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="M40" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" s="5"/>
+      <c r="F41" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H41" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="I41" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="K41" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="L41" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M41" s="20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="3:13" ht="50.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G38" s="29" t="s">
+      <c r="G42" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="30"/>
-      <c r="K38" s="30"/>
-      <c r="L38" s="30"/>
-      <c r="M38" s="31"/>
-    </row>
-    <row r="39" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C39"/>
-      <c r="D39"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="G39" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="30"/>
-      <c r="L39" s="30"/>
-      <c r="M39" s="31"/>
-    </row>
-    <row r="40" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="15"/>
-    </row>
-    <row r="41" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15"/>
-      <c r="M41" s="15"/>
-    </row>
-    <row r="42" spans="3:13" ht="50.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="15"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="31"/>
     </row>
     <row r="43" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
-      <c r="M43" s="15"/>
+      <c r="F43" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="31"/>
     </row>
     <row r="44" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C44" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D44" s="19" t="s">
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="13"/>
+      <c r="M44" s="13"/>
+    </row>
+    <row r="45" spans="3:13" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="13"/>
+      <c r="M45" s="13"/>
+    </row>
+    <row r="46" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
+    </row>
+    <row r="47" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C47"/>
+      <c r="D47"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="13"/>
+      <c r="M47" s="13"/>
+    </row>
+    <row r="48" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C48" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D48" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E48" s="5"/>
+      <c r="F48" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="G48" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="K48" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="M48" s="24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="C49" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="G44" s="20" t="s">
+      <c r="E49" s="5"/>
+      <c r="F49" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="G49" s="24">
+        <v>2</v>
+      </c>
+      <c r="H49" s="24">
+        <v>0</v>
+      </c>
+      <c r="I49" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="J49" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="K49" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="L49" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="M49" s="24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C50"/>
+      <c r="D50"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G50" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="H50" s="30"/>
+      <c r="I50" s="30"/>
+      <c r="J50" s="30"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="31"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="F51" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="G51" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="31"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C53" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E53" s="5"/>
+      <c r="F53" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="G53" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H53" s="5"/>
+    </row>
+    <row r="54" spans="3:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="C54" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E54" s="5"/>
+      <c r="F54" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G54" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C56" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="3:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="C57" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C59" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F59" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G59" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="C60" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="F60" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C62" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D62" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+    </row>
+    <row r="63" spans="3:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="C63" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
+    </row>
+    <row r="65" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C65" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G65" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H44" s="20" t="s">
+      <c r="H65" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="I44" s="20" t="s">
+      <c r="I65" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J44" s="20" t="s">
+      <c r="J65" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="K44" s="20" t="s">
+      <c r="K65" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="L44" s="20" t="s">
+      <c r="L65" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="M44" s="20" t="s">
+      <c r="M65" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="3:13" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="G45" s="20">
-        <v>2</v>
-      </c>
-      <c r="H45" s="20">
-        <v>0</v>
-      </c>
-      <c r="I45" s="20" t="s">
+    <row r="66" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C66" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G66" s="12">
+        <v>3</v>
+      </c>
+      <c r="H66" s="12">
+        <v>0</v>
+      </c>
+      <c r="I66" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="J45" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="K45" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L45" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M45" s="20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C46"/>
-      <c r="D46"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="20" t="s">
+      <c r="J66" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K66" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="L66" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="M66" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="3:13" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F67" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G46" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="H46" s="33"/>
-      <c r="I46" s="33"/>
-      <c r="J46" s="33"/>
-      <c r="K46" s="33"/>
-      <c r="L46" s="33"/>
-      <c r="M46" s="34"/>
-    </row>
-    <row r="47" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F47" s="20" t="s">
+      <c r="G67" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="H67" s="35"/>
+      <c r="I67" s="35"/>
+      <c r="J67" s="35"/>
+      <c r="K67" s="35"/>
+      <c r="L67" s="35"/>
+      <c r="M67" s="36"/>
+    </row>
+    <row r="68" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="F68" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G47" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="H47" s="33"/>
-      <c r="I47" s="33"/>
-      <c r="J47" s="33"/>
-      <c r="K47" s="33"/>
-      <c r="L47" s="33"/>
-      <c r="M47" s="34"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C49" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D49" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="G49" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="H49" s="5"/>
-    </row>
-    <row r="50" spans="3:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="C50" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="D50" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="G50" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="15"/>
-      <c r="L50" s="15"/>
-      <c r="M50" s="15"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C52" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="53" spans="3:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="C53" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C55" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D55" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="F55" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="G55" s="19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="56" spans="3:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="C56" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="F56" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G56" s="20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
-    </row>
-    <row r="58" spans="3:13" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C58" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D58" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="5"/>
-    </row>
-    <row r="59" spans="3:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="C59" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D59" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="5"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C61" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F61" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G61" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H61" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I61" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="J61" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="K61" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="L61" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="M61" s="14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C62" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D62" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="F62" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="G62" s="14">
-        <v>3</v>
-      </c>
-      <c r="H62" s="14">
-        <v>0</v>
-      </c>
-      <c r="I62" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="J62" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="K62" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="L62" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="M62" s="14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="F63" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="G63" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="H63" s="26"/>
-      <c r="I63" s="26"/>
-      <c r="J63" s="26"/>
-      <c r="K63" s="26"/>
-      <c r="L63" s="26"/>
-      <c r="M63" s="27"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="F64" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G64" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="H64" s="26"/>
-      <c r="I64" s="26"/>
-      <c r="J64" s="26"/>
-      <c r="K64" s="26"/>
-      <c r="L64" s="26"/>
-      <c r="M64" s="27"/>
-    </row>
-    <row r="66" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C66" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D66" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="F66" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="G66" s="13" t="s">
+      <c r="G68" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="H68" s="35"/>
+      <c r="I68" s="35"/>
+      <c r="J68" s="35"/>
+      <c r="K68" s="35"/>
+      <c r="L68" s="35"/>
+      <c r="M68" s="36"/>
+    </row>
+    <row r="70" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C70" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="F70" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="G70" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="3:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="C71" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D71" s="12" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="67" spans="3:7" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D67" s="14" t="s">
+      <c r="F71" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G71" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="F67" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="G67" s="14" t="s">
-        <v>86</v>
-      </c>
+    </row>
+    <row r="73" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C73"/>
+      <c r="D73"/>
+    </row>
+    <row r="74" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C74"/>
+      <c r="D74"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="G67:M67"/>
+    <mergeCell ref="G68:M68"/>
+    <mergeCell ref="G27:M27"/>
+    <mergeCell ref="G28:M28"/>
+    <mergeCell ref="G42:M42"/>
+    <mergeCell ref="G43:M43"/>
+    <mergeCell ref="G50:M50"/>
+    <mergeCell ref="G51:M51"/>
+    <mergeCell ref="G19:M19"/>
+    <mergeCell ref="G20:M20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="F1:L1"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="C26:C28"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G15:M15"/>
-    <mergeCell ref="G16:M16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="F1:L1"/>
-    <mergeCell ref="G63:M63"/>
-    <mergeCell ref="G64:M64"/>
-    <mergeCell ref="G23:M23"/>
-    <mergeCell ref="G24:M24"/>
-    <mergeCell ref="G38:M38"/>
-    <mergeCell ref="G39:M39"/>
-    <mergeCell ref="G46:M46"/>
-    <mergeCell ref="G47:M47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
